--- a/public/masterteacher/coordinator/students/Student List Template.xlsx
+++ b/public/masterteacher/coordinator/students/Student List Template.xlsx
@@ -1,75 +1,139 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\OneDrive\Desktop\IS_RPT-SAES\public\masterteacher\coordinator\students\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8292B03-4106-416A-9447-512D0DA773FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
-  <si>
-    <t>SURNAME</t>
-  </si>
-  <si>
-    <t>FIRSTNAME</t>
-  </si>
-  <si>
-    <t>MIDDLENAME</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+  <si>
+    <t>LRN</t>
+  </si>
+  <si>
+    <t>FIRST NAME</t>
+  </si>
+  <si>
+    <t>MIDDLE NAME</t>
+  </si>
+  <si>
+    <t>LAST NAME</t>
   </si>
   <si>
     <t>SUFFIX</t>
   </si>
   <si>
-    <t>GRADE</t>
-  </si>
-  <si>
     <t>SECTION</t>
   </si>
   <si>
-    <t>GUARDIIAN'S SURNAME</t>
-  </si>
-  <si>
-    <t>GUARDIAN'S FIRSTNAME</t>
-  </si>
-  <si>
-    <t>GUARDIAN'S MIDDLENAME</t>
+    <t>PARENT FIRST NAME</t>
+  </si>
+  <si>
+    <t>PARENT MIDDLE NAME</t>
+  </si>
+  <si>
+    <t>PARENT LAST NAME</t>
+  </si>
+  <si>
+    <t>PARENT SUFFIX</t>
   </si>
   <si>
     <t>RELATIONSHIP</t>
   </si>
   <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHONE NUMBER </t>
+  </si>
+  <si>
     <t>ADDRESS</t>
   </si>
   <si>
-    <t>SUBJECT PHONEMIC</t>
-  </si>
-  <si>
-    <t>GUARDIAN'S CONTACT</t>
+    <t>PHONEMIC</t>
+  </si>
+  <si>
+    <t>000000-000000</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Dela</t>
+  </si>
+  <si>
+    <t>Cruz</t>
+  </si>
+  <si>
+    <t>Jr</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Sr</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>juan@gmail.com</t>
+  </si>
+  <si>
+    <t>0912-345-6789</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> House, Street Name, Barangay, City</t>
+  </si>
+  <si>
+    <t>Non-Reader</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;₱&quot;* #,##0_-;\-&quot;₱&quot;* #,##0_-;_-&quot;₱&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -77,24 +141,393 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -102,32 +535,326 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -325,223 +1052,502 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O26"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="20" customWidth="1"/>
+    <col min="7" max="9" width="20" customWidth="1"/>
+    <col min="11" max="11" width="12.6666666666667" customWidth="1"/>
+    <col min="12" max="15" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="26.4" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="6"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:15">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:15">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:15">
+      <c r="A14" s="6"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="F14" s="9"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:15">
+      <c r="A15" s="6"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="F15" s="9"/>
+      <c r="G15"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:15">
+      <c r="A16" s="6"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="F16" s="9"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:15">
+      <c r="A17" s="6"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="F17" s="9"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:15">
+      <c r="A18" s="6"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="9"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:15">
+      <c r="A19" s="6"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="F19" s="9"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="7"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:15">
+      <c r="A20" s="6"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="F20" s="9"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:15">
+      <c r="A21" s="6"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="F21" s="9"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:15">
+      <c r="A22" s="6"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="F22" s="9"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:15">
+      <c r="A23" s="6"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="F23" s="9"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:15">
+      <c r="A24" s="6"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="F24" s="9"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:15">
+      <c r="A25" s="6"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="F25" s="9"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:15">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="L2" r:id="rId1" display="juan@gmail.com" tooltip="mailto:juan@gmail.com"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>